--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -18664,13 +18664,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1440,7 +1444,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1848,7 +1856,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2050,7 +2062,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2151,7 +2167,11 @@
       <c r="AB14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2252,7 +2272,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2755,7 +2779,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2856,7 +2884,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3579,7 +3611,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3680,7 +3716,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4096,7 +4136,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4197,7 +4241,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4298,7 +4346,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4605,7 +4657,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5122,7 +5178,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5223,7 +5283,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5429,7 +5493,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5845,7 +5913,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6051,7 +6123,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6152,7 +6228,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6354,7 +6434,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6455,7 +6539,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6657,7 +6745,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6758,7 +6850,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6859,7 +6955,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7271,7 +7371,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7372,7 +7476,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7679,7 +7787,11 @@
       <c r="AB68" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7780,7 +7892,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7881,7 +7997,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8289,7 +8409,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8390,7 +8514,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8701,7 +8829,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -9424,7 +9556,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9525,7 +9661,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9836,7 +9976,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10042,7 +10186,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10248,7 +10396,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10349,7 +10501,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10450,7 +10606,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10652,7 +10812,11 @@
       <c r="AB97" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10858,7 +11022,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11375,7 +11543,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11783,7 +11955,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12401,7 +12577,11 @@
       <c r="AB114" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -13217,7 +13397,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13423,7 +13607,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13524,7 +13712,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13827,7 +14019,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14033,7 +14229,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14546,7 +14746,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -15261,7 +15465,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -15362,7 +15570,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -15774,7 +15986,11 @@
       <c r="AB147" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC147" s="4" t="inlineStr"/>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -15875,7 +16091,11 @@
       <c r="AB148" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC148" s="4" t="inlineStr"/>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16178,7 +16398,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16380,7 +16604,11 @@
       <c r="AB153" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16481,7 +16709,11 @@
       <c r="AB154" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC154" s="4" t="inlineStr"/>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -16893,7 +17125,11 @@
       <c r="AB158" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC158" s="4" t="inlineStr"/>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -17509,7 +17745,11 @@
       <c r="AB164" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC164" s="4" t="inlineStr"/>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -18018,7 +18258,11 @@
       <c r="AB169" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC169" s="4" t="inlineStr"/>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -18220,7 +18464,11 @@
       <c r="AB171" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -18523,7 +18771,11 @@
       <c r="AB174" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -19036,7 +19288,11 @@
       <c r="AB179" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC179" s="4" t="inlineStr"/>
+      <c r="AC179" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -20264,7 +20520,11 @@
       <c r="AB191" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC191" s="4" t="inlineStr"/>
+      <c r="AC191" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 85 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>0</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2158,8 +2158,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5160,8 +5160,8 @@
       <c r="V43" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>3</v>
+      <c r="W43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>7</v>
@@ -5428,13 +5428,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>6</v>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8180,8 +8180,8 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
         <v>3</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9135,8 +9135,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10492,8 +10492,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10597,8 +10597,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10702,8 +10702,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10957,13 +10957,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10998,14 +10998,14 @@
       <c r="T99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="9" t="n">
-        <v>0</v>
+      <c r="U99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>7</v>
@@ -11478,13 +11478,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>5</v>
@@ -12302,13 +12302,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14202,8 +14202,8 @@
       <c r="S130" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T130" s="9" t="n">
-        <v>0</v>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U130" s="9" t="n">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14430,8 +14430,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -15285,7 +15285,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15355,8 +15355,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15433,10 +15433,10 @@
         <v>2</v>
       </c>
       <c r="R142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S142" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T142" s="10" t="n">
         <v>1</v>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15876,8 +15876,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -17371,13 +17371,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>4</v>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17532,8 +17532,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -17812,7 +17812,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q165" s="9" t="n">
         <v>0</v>
@@ -18797,7 +18797,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18867,8 +18867,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20721,8 +20721,8 @@
       <c r="Y193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z193" s="9" t="n">
-        <v>0</v>
+      <c r="Z193" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA193" s="10" t="n">
         <v>1</v>
@@ -21092,7 +21092,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21257,7 +21257,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -21455,7 +21455,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -21521,7 +21521,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -21620,7 +21620,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21653,7 +21653,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -21884,7 +21884,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21950,7 +21950,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21983,7 +21983,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -22115,7 +22115,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/130/inyear.xlsx
+++ b/docs/d/130/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>
